--- a/CDD/Data temperatures.xlsx
+++ b/CDD/Data temperatures.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\gvaps1\USR6\CHGE\desktop\Fuel desk\CDD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\gvaps1\USR6\CHGE\desktop\Fuel dashboard\CDD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54A51616-EDA1-41F0-9000-1259D33602B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FDA6B47-376F-4087-AEDB-FBB338B51666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{805FC610-D0B7-4151-AF7A-494C14C34CCD}"/>
   </bookViews>
@@ -488,7 +488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDF6C800-FC25-4C64-B3CE-5880A9630BFD}">
-  <dimension ref="A1:E2070"/>
+  <dimension ref="A1:E2072"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.140625" customWidth="1"/>
@@ -548,14 +548,14 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <f>_xll.BDH(B$4,B$6,$B1,$B2,"Dir=V","Per=D","Days=A","Dts=S","cols=2;rows=2064")</f>
+        <f>_xll.BDH(B$4,B$6,$B1,$B2,"Dir=V","Per=D","Days=A","Dts=S","cols=2;rows=2066")</f>
         <v>43831</v>
       </c>
       <c r="B7">
         <v>13.43</v>
       </c>
       <c r="C7">
-        <f>_xll.BDH(C$4,C$6,$B1,$B2,"Dir=V","Per=D","Days=A","Dts=H","cols=1;rows=2064")</f>
+        <f>_xll.BDH(C$4,C$6,$B1,$B2,"Dir=V","Per=D","Days=A","Dts=H","cols=1;rows=2066")</f>
         <v>18.16</v>
       </c>
       <c r="D7">
@@ -39528,7 +39528,7 @@
         <v>38.799999999999997</v>
       </c>
       <c r="D2058">
-        <f t="shared" ref="D2058:E2070" si="58">IF(B2058&gt;18,1,0)</f>
+        <f t="shared" ref="D2058:E2072" si="58">IF(B2058&gt;18,1,0)</f>
         <v>1</v>
       </c>
       <c r="E2058">
@@ -39731,10 +39731,10 @@
         <v>45893</v>
       </c>
       <c r="B2069">
-        <v>30.24</v>
+        <v>30.33</v>
       </c>
       <c r="C2069">
-        <v>36.24</v>
+        <v>35.79</v>
       </c>
       <c r="D2069">
         <f t="shared" si="58"/>
@@ -39750,16 +39750,54 @@
         <v>45894</v>
       </c>
       <c r="B2070">
-        <v>30.24</v>
+        <v>29.58</v>
       </c>
       <c r="C2070">
-        <v>36.24</v>
+        <v>35.549999999999997</v>
       </c>
       <c r="D2070">
         <f t="shared" si="58"/>
         <v>1</v>
       </c>
       <c r="E2070">
+        <f t="shared" si="58"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2071" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2071" s="2">
+        <v>45895</v>
+      </c>
+      <c r="B2071">
+        <v>28.8</v>
+      </c>
+      <c r="C2071">
+        <v>35.97</v>
+      </c>
+      <c r="D2071">
+        <f t="shared" si="58"/>
+        <v>1</v>
+      </c>
+      <c r="E2071">
+        <f t="shared" si="58"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2072" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2072" s="2">
+        <v>45896</v>
+      </c>
+      <c r="B2072">
+        <v>28.8</v>
+      </c>
+      <c r="C2072">
+        <v>35.97</v>
+      </c>
+      <c r="D2072">
+        <f t="shared" si="58"/>
+        <v>1</v>
+      </c>
+      <c r="E2072">
         <f t="shared" si="58"/>
         <v>1</v>
       </c>

--- a/CDD/Data temperatures.xlsx
+++ b/CDD/Data temperatures.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\gvaps1\USR6\CHGE\desktop\Fuel dashboard\CDD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FDA6B47-376F-4087-AEDB-FBB338B51666}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBCDB672-866E-4540-841F-60F073AD53DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{805FC610-D0B7-4151-AF7A-494C14C34CCD}"/>
   </bookViews>
@@ -488,7 +488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDF6C800-FC25-4C64-B3CE-5880A9630BFD}">
-  <dimension ref="A1:E2072"/>
+  <dimension ref="A1:E2085"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.140625" customWidth="1"/>
@@ -548,14 +548,14 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <f>_xll.BDH(B$4,B$6,$B1,$B2,"Dir=V","Per=D","Days=A","Dts=S","cols=2;rows=2066")</f>
+        <f>_xll.BDH(B$4,B$6,$B1,$B2,"Dir=V","Per=D","Days=A","Dts=S","cols=2;rows=2079")</f>
         <v>43831</v>
       </c>
       <c r="B7">
         <v>13.43</v>
       </c>
       <c r="C7">
-        <f>_xll.BDH(C$4,C$6,$B1,$B2,"Dir=V","Per=D","Days=A","Dts=H","cols=1;rows=2066")</f>
+        <f>_xll.BDH(C$4,C$6,$B1,$B2,"Dir=V","Per=D","Days=A","Dts=H","cols=1;rows=2079")</f>
         <v>18.16</v>
       </c>
       <c r="D7">
@@ -39528,7 +39528,7 @@
         <v>38.799999999999997</v>
       </c>
       <c r="D2058">
-        <f t="shared" ref="D2058:E2072" si="58">IF(B2058&gt;18,1,0)</f>
+        <f t="shared" ref="D2058:E2073" si="58">IF(B2058&gt;18,1,0)</f>
         <v>1</v>
       </c>
       <c r="E2058">
@@ -39788,10 +39788,10 @@
         <v>45896</v>
       </c>
       <c r="B2072">
-        <v>28.8</v>
+        <v>28.48</v>
       </c>
       <c r="C2072">
-        <v>35.97</v>
+        <v>35.85</v>
       </c>
       <c r="D2072">
         <f t="shared" si="58"/>
@@ -39799,6 +39799,253 @@
       </c>
       <c r="E2072">
         <f t="shared" si="58"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2073" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2073" s="2">
+        <v>45897</v>
+      </c>
+      <c r="B2073">
+        <v>27.83</v>
+      </c>
+      <c r="C2073">
+        <v>35.369999999999997</v>
+      </c>
+      <c r="D2073">
+        <f t="shared" si="58"/>
+        <v>1</v>
+      </c>
+      <c r="E2073">
+        <f t="shared" si="58"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2074" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2074" s="2">
+        <v>45898</v>
+      </c>
+      <c r="B2074">
+        <v>29.15</v>
+      </c>
+      <c r="C2074">
+        <v>35.93</v>
+      </c>
+      <c r="D2074">
+        <f t="shared" ref="D2074:E2085" si="59">IF(B2074&gt;18,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="E2074">
+        <f t="shared" si="59"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2075" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2075" s="2">
+        <v>45899</v>
+      </c>
+      <c r="B2075">
+        <v>28.77</v>
+      </c>
+      <c r="C2075">
+        <v>36.07</v>
+      </c>
+      <c r="D2075">
+        <f t="shared" si="59"/>
+        <v>1</v>
+      </c>
+      <c r="E2075">
+        <f t="shared" si="59"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2076" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2076" s="2">
+        <v>45900</v>
+      </c>
+      <c r="B2076">
+        <v>29.19</v>
+      </c>
+      <c r="C2076">
+        <v>36.72</v>
+      </c>
+      <c r="D2076">
+        <f t="shared" si="59"/>
+        <v>1</v>
+      </c>
+      <c r="E2076">
+        <f t="shared" si="59"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2077" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2077" s="2">
+        <v>45901</v>
+      </c>
+      <c r="B2077">
+        <v>29.17</v>
+      </c>
+      <c r="C2077">
+        <v>36.04</v>
+      </c>
+      <c r="D2077">
+        <f t="shared" si="59"/>
+        <v>1</v>
+      </c>
+      <c r="E2077">
+        <f t="shared" si="59"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2078" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2078" s="2">
+        <v>45902</v>
+      </c>
+      <c r="B2078">
+        <v>29.15</v>
+      </c>
+      <c r="C2078">
+        <v>35.200000000000003</v>
+      </c>
+      <c r="D2078">
+        <f t="shared" si="59"/>
+        <v>1</v>
+      </c>
+      <c r="E2078">
+        <f t="shared" si="59"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2079" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2079" s="2">
+        <v>45903</v>
+      </c>
+      <c r="B2079">
+        <v>28.56</v>
+      </c>
+      <c r="C2079">
+        <v>35.47</v>
+      </c>
+      <c r="D2079">
+        <f t="shared" si="59"/>
+        <v>1</v>
+      </c>
+      <c r="E2079">
+        <f t="shared" si="59"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2080" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2080" s="2">
+        <v>45904</v>
+      </c>
+      <c r="B2080">
+        <v>28.92</v>
+      </c>
+      <c r="C2080">
+        <v>35.200000000000003</v>
+      </c>
+      <c r="D2080">
+        <f t="shared" si="59"/>
+        <v>1</v>
+      </c>
+      <c r="E2080">
+        <f t="shared" si="59"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2081" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2081" s="2">
+        <v>45905</v>
+      </c>
+      <c r="B2081">
+        <v>28.78</v>
+      </c>
+      <c r="C2081">
+        <v>35.04</v>
+      </c>
+      <c r="D2081">
+        <f t="shared" si="59"/>
+        <v>1</v>
+      </c>
+      <c r="E2081">
+        <f t="shared" si="59"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2082" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2082" s="2">
+        <v>45906</v>
+      </c>
+      <c r="B2082">
+        <v>28.16</v>
+      </c>
+      <c r="C2082">
+        <v>35.46</v>
+      </c>
+      <c r="D2082">
+        <f t="shared" si="59"/>
+        <v>1</v>
+      </c>
+      <c r="E2082">
+        <f t="shared" si="59"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2083" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2083" s="2">
+        <v>45907</v>
+      </c>
+      <c r="B2083">
+        <v>27.62</v>
+      </c>
+      <c r="C2083">
+        <v>35.67</v>
+      </c>
+      <c r="D2083">
+        <f t="shared" si="59"/>
+        <v>1</v>
+      </c>
+      <c r="E2083">
+        <f t="shared" si="59"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2084" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2084" s="2">
+        <v>45908</v>
+      </c>
+      <c r="B2084">
+        <v>27.62</v>
+      </c>
+      <c r="C2084">
+        <v>35.67</v>
+      </c>
+      <c r="D2084">
+        <f t="shared" si="59"/>
+        <v>1</v>
+      </c>
+      <c r="E2084">
+        <f t="shared" si="59"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2085" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2085" s="2">
+        <v>45909</v>
+      </c>
+      <c r="B2085">
+        <v>27.62</v>
+      </c>
+      <c r="C2085">
+        <v>35.67</v>
+      </c>
+      <c r="D2085">
+        <f t="shared" si="59"/>
+        <v>1</v>
+      </c>
+      <c r="E2085">
+        <f t="shared" si="59"/>
         <v>1</v>
       </c>
     </row>

--- a/CDD/Data temperatures.xlsx
+++ b/CDD/Data temperatures.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\gvaps1\USR6\CHGE\desktop\Fuel dashboard\CDD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBCDB672-866E-4540-841F-60F073AD53DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D23ADFE7-01AE-46F8-8679-854951C289C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{805FC610-D0B7-4151-AF7A-494C14C34CCD}"/>
   </bookViews>
@@ -488,7 +488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDF6C800-FC25-4C64-B3CE-5880A9630BFD}">
-  <dimension ref="A1:E2085"/>
+  <dimension ref="A1:E2091"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.140625" customWidth="1"/>
@@ -548,14 +548,14 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <f>_xll.BDH(B$4,B$6,$B1,$B2,"Dir=V","Per=D","Days=A","Dts=S","cols=2;rows=2079")</f>
+        <f>_xll.BDH(B$4,B$6,$B1,$B2,"Dir=V","Per=D","Days=A","Dts=S","cols=2;rows=2085")</f>
         <v>43831</v>
       </c>
       <c r="B7">
         <v>13.43</v>
       </c>
       <c r="C7">
-        <f>_xll.BDH(C$4,C$6,$B1,$B2,"Dir=V","Per=D","Days=A","Dts=H","cols=1;rows=2079")</f>
+        <f>_xll.BDH(C$4,C$6,$B1,$B2,"Dir=V","Per=D","Days=A","Dts=H","cols=1;rows=2085")</f>
         <v>18.16</v>
       </c>
       <c r="D7">
@@ -39832,7 +39832,7 @@
         <v>35.93</v>
       </c>
       <c r="D2074">
-        <f t="shared" ref="D2074:E2085" si="59">IF(B2074&gt;18,1,0)</f>
+        <f t="shared" ref="D2074:E2089" si="59">IF(B2074&gt;18,1,0)</f>
         <v>1</v>
       </c>
       <c r="E2074">
@@ -40016,10 +40016,10 @@
         <v>45908</v>
       </c>
       <c r="B2084">
-        <v>27.62</v>
+        <v>27.28</v>
       </c>
       <c r="C2084">
-        <v>35.67</v>
+        <v>35.89</v>
       </c>
       <c r="D2084">
         <f t="shared" si="59"/>
@@ -40035,10 +40035,10 @@
         <v>45909</v>
       </c>
       <c r="B2085">
-        <v>27.62</v>
+        <v>26.99</v>
       </c>
       <c r="C2085">
-        <v>35.67</v>
+        <v>35.9</v>
       </c>
       <c r="D2085">
         <f t="shared" si="59"/>
@@ -40046,6 +40046,120 @@
       </c>
       <c r="E2085">
         <f t="shared" si="59"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2086" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2086" s="2">
+        <v>45910</v>
+      </c>
+      <c r="B2086">
+        <v>26.98</v>
+      </c>
+      <c r="C2086">
+        <v>35.18</v>
+      </c>
+      <c r="D2086">
+        <f t="shared" si="59"/>
+        <v>1</v>
+      </c>
+      <c r="E2086">
+        <f t="shared" si="59"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2087" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2087" s="2">
+        <v>45911</v>
+      </c>
+      <c r="B2087">
+        <v>27.33</v>
+      </c>
+      <c r="C2087">
+        <v>35.17</v>
+      </c>
+      <c r="D2087">
+        <f t="shared" si="59"/>
+        <v>1</v>
+      </c>
+      <c r="E2087">
+        <f t="shared" si="59"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2088" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2088" s="2">
+        <v>45912</v>
+      </c>
+      <c r="B2088">
+        <v>27.78</v>
+      </c>
+      <c r="C2088">
+        <v>35.36</v>
+      </c>
+      <c r="D2088">
+        <f t="shared" si="59"/>
+        <v>1</v>
+      </c>
+      <c r="E2088">
+        <f t="shared" si="59"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2089" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2089" s="2">
+        <v>45913</v>
+      </c>
+      <c r="B2089">
+        <v>28.29</v>
+      </c>
+      <c r="C2089">
+        <v>35.25</v>
+      </c>
+      <c r="D2089">
+        <f t="shared" si="59"/>
+        <v>1</v>
+      </c>
+      <c r="E2089">
+        <f t="shared" si="59"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2090" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2090" s="2">
+        <v>45914</v>
+      </c>
+      <c r="B2090">
+        <v>28.44</v>
+      </c>
+      <c r="C2090">
+        <v>34.520000000000003</v>
+      </c>
+      <c r="D2090">
+        <f t="shared" ref="D2090:E2091" si="60">IF(B2090&gt;18,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="E2090">
+        <f t="shared" si="60"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2091" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2091" s="2">
+        <v>45915</v>
+      </c>
+      <c r="B2091">
+        <v>28.44</v>
+      </c>
+      <c r="C2091">
+        <v>34.520000000000003</v>
+      </c>
+      <c r="D2091">
+        <f t="shared" si="60"/>
+        <v>1</v>
+      </c>
+      <c r="E2091">
+        <f t="shared" si="60"/>
         <v>1</v>
       </c>
     </row>

--- a/CDD/Data temperatures.xlsx
+++ b/CDD/Data temperatures.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\gvaps1\USR6\CHGE\desktop\Fuel dashboard\CDD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D23ADFE7-01AE-46F8-8679-854951C289C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{228FBD98-B104-4B98-B9D1-F6AC15AB7F03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{805FC610-D0B7-4151-AF7A-494C14C34CCD}"/>
   </bookViews>
@@ -488,7 +488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDF6C800-FC25-4C64-B3CE-5880A9630BFD}">
-  <dimension ref="A1:E2091"/>
+  <dimension ref="A1:E2095"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.140625" customWidth="1"/>
@@ -548,14 +548,14 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <f>_xll.BDH(B$4,B$6,$B1,$B2,"Dir=V","Per=D","Days=A","Dts=S","cols=2;rows=2085")</f>
+        <f>_xll.BDH(B$4,B$6,$B1,$B2,"Dir=V","Per=D","Days=A","Dts=S","cols=2;rows=2089")</f>
         <v>43831</v>
       </c>
       <c r="B7">
         <v>13.43</v>
       </c>
       <c r="C7">
-        <f>_xll.BDH(C$4,C$6,$B1,$B2,"Dir=V","Per=D","Days=A","Dts=H","cols=1;rows=2085")</f>
+        <f>_xll.BDH(C$4,C$6,$B1,$B2,"Dir=V","Per=D","Days=A","Dts=H","cols=1;rows=2089")</f>
         <v>18.16</v>
       </c>
       <c r="D7">
@@ -40136,7 +40136,7 @@
         <v>34.520000000000003</v>
       </c>
       <c r="D2090">
-        <f t="shared" ref="D2090:E2091" si="60">IF(B2090&gt;18,1,0)</f>
+        <f t="shared" ref="D2090:E2095" si="60">IF(B2090&gt;18,1,0)</f>
         <v>1</v>
       </c>
       <c r="E2090">
@@ -40149,16 +40149,92 @@
         <v>45915</v>
       </c>
       <c r="B2091">
-        <v>28.44</v>
+        <v>27.53</v>
       </c>
       <c r="C2091">
-        <v>34.520000000000003</v>
+        <v>34.32</v>
       </c>
       <c r="D2091">
         <f t="shared" si="60"/>
         <v>1</v>
       </c>
       <c r="E2091">
+        <f t="shared" si="60"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2092" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2092" s="2">
+        <v>45916</v>
+      </c>
+      <c r="B2092">
+        <v>27.08</v>
+      </c>
+      <c r="C2092">
+        <v>34.090000000000003</v>
+      </c>
+      <c r="D2092">
+        <f t="shared" si="60"/>
+        <v>1</v>
+      </c>
+      <c r="E2092">
+        <f t="shared" si="60"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2093" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2093" s="2">
+        <v>45917</v>
+      </c>
+      <c r="B2093">
+        <v>27.27</v>
+      </c>
+      <c r="C2093">
+        <v>33.909999999999997</v>
+      </c>
+      <c r="D2093">
+        <f t="shared" si="60"/>
+        <v>1</v>
+      </c>
+      <c r="E2093">
+        <f t="shared" si="60"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2094" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2094" s="2">
+        <v>45918</v>
+      </c>
+      <c r="B2094">
+        <v>27.27</v>
+      </c>
+      <c r="C2094">
+        <v>33.909999999999997</v>
+      </c>
+      <c r="D2094">
+        <f t="shared" si="60"/>
+        <v>1</v>
+      </c>
+      <c r="E2094">
+        <f t="shared" si="60"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2095" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2095" s="2">
+        <v>45919</v>
+      </c>
+      <c r="B2095">
+        <v>27.27</v>
+      </c>
+      <c r="C2095">
+        <v>33.909999999999997</v>
+      </c>
+      <c r="D2095">
+        <f t="shared" si="60"/>
+        <v>1</v>
+      </c>
+      <c r="E2095">
         <f t="shared" si="60"/>
         <v>1</v>
       </c>

--- a/CDD/Data temperatures.xlsx
+++ b/CDD/Data temperatures.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\gvaps1\USR6\CHGE\desktop\Fuel dashboard\CDD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{228FBD98-B104-4B98-B9D1-F6AC15AB7F03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67B4A065-FB95-4254-831F-3BDEA326FB13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{805FC610-D0B7-4151-AF7A-494C14C34CCD}"/>
   </bookViews>
@@ -488,7 +488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDF6C800-FC25-4C64-B3CE-5880A9630BFD}">
-  <dimension ref="A1:E2095"/>
+  <dimension ref="A1:E2098"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.140625" customWidth="1"/>
@@ -548,14 +548,14 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <f>_xll.BDH(B$4,B$6,$B1,$B2,"Dir=V","Per=D","Days=A","Dts=S","cols=2;rows=2089")</f>
+        <f>_xll.BDH(B$4,B$6,$B1,$B2,"Dir=V","Per=D","Days=A","Dts=S","cols=2;rows=2092")</f>
         <v>43831</v>
       </c>
       <c r="B7">
         <v>13.43</v>
       </c>
       <c r="C7">
-        <f>_xll.BDH(C$4,C$6,$B1,$B2,"Dir=V","Per=D","Days=A","Dts=H","cols=1;rows=2089")</f>
+        <f>_xll.BDH(C$4,C$6,$B1,$B2,"Dir=V","Per=D","Days=A","Dts=H","cols=1;rows=2092")</f>
         <v>18.16</v>
       </c>
       <c r="D7">
@@ -40136,7 +40136,7 @@
         <v>34.520000000000003</v>
       </c>
       <c r="D2090">
-        <f t="shared" ref="D2090:E2095" si="60">IF(B2090&gt;18,1,0)</f>
+        <f t="shared" ref="D2090:E2098" si="60">IF(B2090&gt;18,1,0)</f>
         <v>1</v>
       </c>
       <c r="E2090">
@@ -40206,10 +40206,10 @@
         <v>45918</v>
       </c>
       <c r="B2094">
-        <v>27.27</v>
+        <v>27.58</v>
       </c>
       <c r="C2094">
-        <v>33.909999999999997</v>
+        <v>34.46</v>
       </c>
       <c r="D2094">
         <f t="shared" si="60"/>
@@ -40225,16 +40225,73 @@
         <v>45919</v>
       </c>
       <c r="B2095">
-        <v>27.27</v>
+        <v>27.22</v>
       </c>
       <c r="C2095">
-        <v>33.909999999999997</v>
+        <v>35.450000000000003</v>
       </c>
       <c r="D2095">
         <f t="shared" si="60"/>
         <v>1</v>
       </c>
       <c r="E2095">
+        <f t="shared" si="60"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2096" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2096" s="2">
+        <v>45920</v>
+      </c>
+      <c r="B2096">
+        <v>27.01</v>
+      </c>
+      <c r="C2096">
+        <v>35.36</v>
+      </c>
+      <c r="D2096">
+        <f t="shared" si="60"/>
+        <v>1</v>
+      </c>
+      <c r="E2096">
+        <f t="shared" si="60"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2097" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2097" s="2">
+        <v>45921</v>
+      </c>
+      <c r="B2097">
+        <v>27.01</v>
+      </c>
+      <c r="C2097">
+        <v>35.36</v>
+      </c>
+      <c r="D2097">
+        <f t="shared" si="60"/>
+        <v>1</v>
+      </c>
+      <c r="E2097">
+        <f t="shared" si="60"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2098" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2098" s="2">
+        <v>45922</v>
+      </c>
+      <c r="B2098">
+        <v>27.01</v>
+      </c>
+      <c r="C2098">
+        <v>35.36</v>
+      </c>
+      <c r="D2098">
+        <f t="shared" si="60"/>
+        <v>1</v>
+      </c>
+      <c r="E2098">
         <f t="shared" si="60"/>
         <v>1</v>
       </c>

--- a/CDD/Data temperatures.xlsx
+++ b/CDD/Data temperatures.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\gvaps1\USR6\CHGE\desktop\Fuel dashboard\CDD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67B4A065-FB95-4254-831F-3BDEA326FB13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2AFF9F7-9218-4836-9F52-636F646C38C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{805FC610-D0B7-4151-AF7A-494C14C34CCD}"/>
   </bookViews>
@@ -488,7 +488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDF6C800-FC25-4C64-B3CE-5880A9630BFD}">
-  <dimension ref="A1:E2098"/>
+  <dimension ref="A1:E2101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.140625" customWidth="1"/>
@@ -548,14 +548,14 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <f>_xll.BDH(B$4,B$6,$B1,$B2,"Dir=V","Per=D","Days=A","Dts=S","cols=2;rows=2092")</f>
+        <f>_xll.BDH(B$4,B$6,$B1,$B2,"Dir=V","Per=D","Days=A","Dts=S","cols=2;rows=2095")</f>
         <v>43831</v>
       </c>
       <c r="B7">
         <v>13.43</v>
       </c>
       <c r="C7">
-        <f>_xll.BDH(C$4,C$6,$B1,$B2,"Dir=V","Per=D","Days=A","Dts=H","cols=1;rows=2092")</f>
+        <f>_xll.BDH(C$4,C$6,$B1,$B2,"Dir=V","Per=D","Days=A","Dts=H","cols=1;rows=2095")</f>
         <v>18.16</v>
       </c>
       <c r="D7">
@@ -40136,7 +40136,7 @@
         <v>34.520000000000003</v>
       </c>
       <c r="D2090">
-        <f t="shared" ref="D2090:E2098" si="60">IF(B2090&gt;18,1,0)</f>
+        <f t="shared" ref="D2090:E2101" si="60">IF(B2090&gt;18,1,0)</f>
         <v>1</v>
       </c>
       <c r="E2090">
@@ -40263,10 +40263,10 @@
         <v>45921</v>
       </c>
       <c r="B2097">
-        <v>27.01</v>
+        <v>26.15</v>
       </c>
       <c r="C2097">
-        <v>35.36</v>
+        <v>34.770000000000003</v>
       </c>
       <c r="D2097">
         <f t="shared" si="60"/>
@@ -40282,16 +40282,73 @@
         <v>45922</v>
       </c>
       <c r="B2098">
-        <v>27.01</v>
+        <v>25.95</v>
       </c>
       <c r="C2098">
-        <v>35.36</v>
+        <v>33.86</v>
       </c>
       <c r="D2098">
         <f t="shared" si="60"/>
         <v>1</v>
       </c>
       <c r="E2098">
+        <f t="shared" si="60"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2099" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2099" s="2">
+        <v>45923</v>
+      </c>
+      <c r="B2099">
+        <v>26.44</v>
+      </c>
+      <c r="C2099">
+        <v>34.06</v>
+      </c>
+      <c r="D2099">
+        <f t="shared" si="60"/>
+        <v>1</v>
+      </c>
+      <c r="E2099">
+        <f t="shared" si="60"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2100" s="2">
+        <v>45924</v>
+      </c>
+      <c r="B2100">
+        <v>26.44</v>
+      </c>
+      <c r="C2100">
+        <v>34.06</v>
+      </c>
+      <c r="D2100">
+        <f t="shared" si="60"/>
+        <v>1</v>
+      </c>
+      <c r="E2100">
+        <f t="shared" si="60"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2101" s="2">
+        <v>45925</v>
+      </c>
+      <c r="B2101">
+        <v>26.44</v>
+      </c>
+      <c r="C2101">
+        <v>34.06</v>
+      </c>
+      <c r="D2101">
+        <f t="shared" si="60"/>
+        <v>1</v>
+      </c>
+      <c r="E2101">
         <f t="shared" si="60"/>
         <v>1</v>
       </c>

--- a/CDD/Data temperatures.xlsx
+++ b/CDD/Data temperatures.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\gvaps1\USR6\CHGE\desktop\Fuel dashboard\CDD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2AFF9F7-9218-4836-9F52-636F646C38C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4335988-8B4A-415E-8A3D-49AFE8063B9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{805FC610-D0B7-4151-AF7A-494C14C34CCD}"/>
   </bookViews>
@@ -488,7 +488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDF6C800-FC25-4C64-B3CE-5880A9630BFD}">
-  <dimension ref="A1:E2101"/>
+  <dimension ref="A1:E2106"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.140625" customWidth="1"/>
@@ -548,14 +548,14 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <f>_xll.BDH(B$4,B$6,$B1,$B2,"Dir=V","Per=D","Days=A","Dts=S","cols=2;rows=2095")</f>
+        <f>_xll.BDH(B$4,B$6,$B1,$B2,"Dir=V","Per=D","Days=A","Dts=S","cols=2;rows=2100")</f>
         <v>43831</v>
       </c>
       <c r="B7">
         <v>13.43</v>
       </c>
       <c r="C7">
-        <f>_xll.BDH(C$4,C$6,$B1,$B2,"Dir=V","Per=D","Days=A","Dts=H","cols=1;rows=2095")</f>
+        <f>_xll.BDH(C$4,C$6,$B1,$B2,"Dir=V","Per=D","Days=A","Dts=H","cols=1;rows=2100")</f>
         <v>18.16</v>
       </c>
       <c r="D7">
@@ -40136,7 +40136,7 @@
         <v>34.520000000000003</v>
       </c>
       <c r="D2090">
-        <f t="shared" ref="D2090:E2101" si="60">IF(B2090&gt;18,1,0)</f>
+        <f t="shared" ref="D2090:E2105" si="60">IF(B2090&gt;18,1,0)</f>
         <v>1</v>
       </c>
       <c r="E2090">
@@ -40320,10 +40320,10 @@
         <v>45924</v>
       </c>
       <c r="B2100">
-        <v>26.44</v>
+        <v>26.12</v>
       </c>
       <c r="C2100">
-        <v>34.06</v>
+        <v>32.99</v>
       </c>
       <c r="D2100">
         <f t="shared" si="60"/>
@@ -40339,10 +40339,10 @@
         <v>45925</v>
       </c>
       <c r="B2101">
-        <v>26.44</v>
+        <v>25.48</v>
       </c>
       <c r="C2101">
-        <v>34.06</v>
+        <v>32.72</v>
       </c>
       <c r="D2101">
         <f t="shared" si="60"/>
@@ -40350,6 +40350,101 @@
       </c>
       <c r="E2101">
         <f t="shared" si="60"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2102" s="2">
+        <v>45926</v>
+      </c>
+      <c r="B2102">
+        <v>25.76</v>
+      </c>
+      <c r="C2102">
+        <v>33.28</v>
+      </c>
+      <c r="D2102">
+        <f t="shared" si="60"/>
+        <v>1</v>
+      </c>
+      <c r="E2102">
+        <f t="shared" si="60"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2103" s="2">
+        <v>45927</v>
+      </c>
+      <c r="B2103">
+        <v>25.72</v>
+      </c>
+      <c r="C2103">
+        <v>33.72</v>
+      </c>
+      <c r="D2103">
+        <f t="shared" si="60"/>
+        <v>1</v>
+      </c>
+      <c r="E2103">
+        <f t="shared" si="60"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2104" s="2">
+        <v>45928</v>
+      </c>
+      <c r="B2104">
+        <v>25.61</v>
+      </c>
+      <c r="C2104">
+        <v>33.86</v>
+      </c>
+      <c r="D2104">
+        <f t="shared" si="60"/>
+        <v>1</v>
+      </c>
+      <c r="E2104">
+        <f t="shared" si="60"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2105" s="2">
+        <v>45929</v>
+      </c>
+      <c r="B2105">
+        <v>25.61</v>
+      </c>
+      <c r="C2105">
+        <v>33.86</v>
+      </c>
+      <c r="D2105">
+        <f t="shared" si="60"/>
+        <v>1</v>
+      </c>
+      <c r="E2105">
+        <f t="shared" si="60"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2106" s="2">
+        <v>45930</v>
+      </c>
+      <c r="B2106">
+        <v>25.61</v>
+      </c>
+      <c r="C2106">
+        <v>33.86</v>
+      </c>
+      <c r="D2106">
+        <f t="shared" ref="D2106:E2106" si="61">IF(B2106&gt;18,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="E2106">
+        <f t="shared" si="61"/>
         <v>1</v>
       </c>
     </row>

--- a/CDD/Data temperatures.xlsx
+++ b/CDD/Data temperatures.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\gvaps1\USR6\CHGE\desktop\Fuel dashboard\CDD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4335988-8B4A-415E-8A3D-49AFE8063B9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A562A2FD-BE2A-4A2D-AE01-7EA1081CC114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{805FC610-D0B7-4151-AF7A-494C14C34CCD}"/>
   </bookViews>
@@ -488,7 +488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDF6C800-FC25-4C64-B3CE-5880A9630BFD}">
-  <dimension ref="A1:E2106"/>
+  <dimension ref="A1:E2113"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.140625" customWidth="1"/>
@@ -548,14 +548,14 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <f>_xll.BDH(B$4,B$6,$B1,$B2,"Dir=V","Per=D","Days=A","Dts=S","cols=2;rows=2100")</f>
+        <f>_xll.BDH(B$4,B$6,$B1,$B2,"Dir=V","Per=D","Days=A","Dts=S","cols=2;rows=2107")</f>
         <v>43831</v>
       </c>
       <c r="B7">
         <v>13.43</v>
       </c>
       <c r="C7">
-        <f>_xll.BDH(C$4,C$6,$B1,$B2,"Dir=V","Per=D","Days=A","Dts=H","cols=1;rows=2100")</f>
+        <f>_xll.BDH(C$4,C$6,$B1,$B2,"Dir=V","Per=D","Days=A","Dts=H","cols=1;rows=2107")</f>
         <v>18.16</v>
       </c>
       <c r="D7">
@@ -40415,10 +40415,10 @@
         <v>45929</v>
       </c>
       <c r="B2105">
-        <v>25.61</v>
+        <v>25.6</v>
       </c>
       <c r="C2105">
-        <v>33.86</v>
+        <v>33.49</v>
       </c>
       <c r="D2105">
         <f t="shared" si="60"/>
@@ -40434,16 +40434,149 @@
         <v>45930</v>
       </c>
       <c r="B2106">
-        <v>25.61</v>
+        <v>26.1</v>
       </c>
       <c r="C2106">
-        <v>33.86</v>
+        <v>33.47</v>
       </c>
       <c r="D2106">
-        <f t="shared" ref="D2106:E2106" si="61">IF(B2106&gt;18,1,0)</f>
+        <f t="shared" ref="D2106:E2113" si="61">IF(B2106&gt;18,1,0)</f>
         <v>1</v>
       </c>
       <c r="E2106">
+        <f t="shared" si="61"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2107" s="2">
+        <v>45931</v>
+      </c>
+      <c r="B2107">
+        <v>25.64</v>
+      </c>
+      <c r="C2107">
+        <v>32.61</v>
+      </c>
+      <c r="D2107">
+        <f t="shared" si="61"/>
+        <v>1</v>
+      </c>
+      <c r="E2107">
+        <f t="shared" si="61"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2108" s="2">
+        <v>45932</v>
+      </c>
+      <c r="B2108">
+        <v>27.06</v>
+      </c>
+      <c r="C2108">
+        <v>31.54</v>
+      </c>
+      <c r="D2108">
+        <f t="shared" si="61"/>
+        <v>1</v>
+      </c>
+      <c r="E2108">
+        <f t="shared" si="61"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2109" s="2">
+        <v>45933</v>
+      </c>
+      <c r="B2109">
+        <v>27.08</v>
+      </c>
+      <c r="C2109">
+        <v>30.75</v>
+      </c>
+      <c r="D2109">
+        <f t="shared" si="61"/>
+        <v>1</v>
+      </c>
+      <c r="E2109">
+        <f t="shared" si="61"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2110" s="2">
+        <v>45934</v>
+      </c>
+      <c r="B2110">
+        <v>26.44</v>
+      </c>
+      <c r="C2110">
+        <v>30.13</v>
+      </c>
+      <c r="D2110">
+        <f t="shared" si="61"/>
+        <v>1</v>
+      </c>
+      <c r="E2110">
+        <f t="shared" si="61"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2111" s="2">
+        <v>45935</v>
+      </c>
+      <c r="B2111">
+        <v>25.06</v>
+      </c>
+      <c r="C2111">
+        <v>30.05</v>
+      </c>
+      <c r="D2111">
+        <f t="shared" si="61"/>
+        <v>1</v>
+      </c>
+      <c r="E2111">
+        <f t="shared" si="61"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2112" s="2">
+        <v>45936</v>
+      </c>
+      <c r="B2112">
+        <v>25.06</v>
+      </c>
+      <c r="C2112">
+        <v>30.05</v>
+      </c>
+      <c r="D2112">
+        <f t="shared" si="61"/>
+        <v>1</v>
+      </c>
+      <c r="E2112">
+        <f t="shared" si="61"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2113" s="2">
+        <v>45937</v>
+      </c>
+      <c r="B2113">
+        <v>25.06</v>
+      </c>
+      <c r="C2113">
+        <v>30.05</v>
+      </c>
+      <c r="D2113">
+        <f t="shared" si="61"/>
+        <v>1</v>
+      </c>
+      <c r="E2113">
         <f t="shared" si="61"/>
         <v>1</v>
       </c>

--- a/CDD/Data temperatures.xlsx
+++ b/CDD/Data temperatures.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\gvaps1\USR6\CHGE\desktop\Fuel dashboard\CDD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A562A2FD-BE2A-4A2D-AE01-7EA1081CC114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD73DB6E-03A8-43FF-8608-1A58DF10AEE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{805FC610-D0B7-4151-AF7A-494C14C34CCD}"/>
   </bookViews>
@@ -488,7 +488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDF6C800-FC25-4C64-B3CE-5880A9630BFD}">
-  <dimension ref="A1:E2113"/>
+  <dimension ref="A1:E2119"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.140625" customWidth="1"/>
@@ -548,14 +548,14 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <f>_xll.BDH(B$4,B$6,$B1,$B2,"Dir=V","Per=D","Days=A","Dts=S","cols=2;rows=2107")</f>
+        <f>_xll.BDH(B$4,B$6,$B1,$B2,"Dir=V","Per=D","Days=A","Dts=S","cols=2;rows=2113")</f>
         <v>43831</v>
       </c>
       <c r="B7">
         <v>13.43</v>
       </c>
       <c r="C7">
-        <f>_xll.BDH(C$4,C$6,$B1,$B2,"Dir=V","Per=D","Days=A","Dts=H","cols=1;rows=2107")</f>
+        <f>_xll.BDH(C$4,C$6,$B1,$B2,"Dir=V","Per=D","Days=A","Dts=H","cols=1;rows=2113")</f>
         <v>18.16</v>
       </c>
       <c r="D7">
@@ -40440,7 +40440,7 @@
         <v>33.47</v>
       </c>
       <c r="D2106">
-        <f t="shared" ref="D2106:E2113" si="61">IF(B2106&gt;18,1,0)</f>
+        <f t="shared" ref="D2106:E2119" si="61">IF(B2106&gt;18,1,0)</f>
         <v>1</v>
       </c>
       <c r="E2106">
@@ -40548,10 +40548,10 @@
         <v>45936</v>
       </c>
       <c r="B2112">
-        <v>25.06</v>
+        <v>24.03</v>
       </c>
       <c r="C2112">
-        <v>30.05</v>
+        <v>29.71</v>
       </c>
       <c r="D2112">
         <f t="shared" si="61"/>
@@ -40567,16 +40567,130 @@
         <v>45937</v>
       </c>
       <c r="B2113">
-        <v>25.06</v>
+        <v>25.39</v>
       </c>
       <c r="C2113">
-        <v>30.05</v>
+        <v>29.82</v>
       </c>
       <c r="D2113">
         <f t="shared" si="61"/>
         <v>1</v>
       </c>
       <c r="E2113">
+        <f t="shared" si="61"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2114" s="2">
+        <v>45938</v>
+      </c>
+      <c r="B2114">
+        <v>26.02</v>
+      </c>
+      <c r="C2114">
+        <v>29.82</v>
+      </c>
+      <c r="D2114">
+        <f t="shared" si="61"/>
+        <v>1</v>
+      </c>
+      <c r="E2114">
+        <f t="shared" si="61"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2115" s="2">
+        <v>45939</v>
+      </c>
+      <c r="B2115">
+        <v>24.25</v>
+      </c>
+      <c r="C2115">
+        <v>30.14</v>
+      </c>
+      <c r="D2115">
+        <f t="shared" si="61"/>
+        <v>1</v>
+      </c>
+      <c r="E2115">
+        <f t="shared" si="61"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2116" s="2">
+        <v>45940</v>
+      </c>
+      <c r="B2116">
+        <v>23.14</v>
+      </c>
+      <c r="C2116">
+        <v>30.13</v>
+      </c>
+      <c r="D2116">
+        <f t="shared" si="61"/>
+        <v>1</v>
+      </c>
+      <c r="E2116">
+        <f t="shared" si="61"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2117" s="2">
+        <v>45941</v>
+      </c>
+      <c r="B2117">
+        <v>23.04</v>
+      </c>
+      <c r="C2117">
+        <v>29.34</v>
+      </c>
+      <c r="D2117">
+        <f t="shared" si="61"/>
+        <v>1</v>
+      </c>
+      <c r="E2117">
+        <f t="shared" si="61"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2118" s="2">
+        <v>45942</v>
+      </c>
+      <c r="B2118">
+        <v>23.1</v>
+      </c>
+      <c r="C2118">
+        <v>28.93</v>
+      </c>
+      <c r="D2118">
+        <f t="shared" si="61"/>
+        <v>1</v>
+      </c>
+      <c r="E2118">
+        <f t="shared" si="61"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2119" s="2">
+        <v>45943</v>
+      </c>
+      <c r="B2119">
+        <v>23.1</v>
+      </c>
+      <c r="C2119">
+        <v>28.93</v>
+      </c>
+      <c r="D2119">
+        <f t="shared" si="61"/>
+        <v>1</v>
+      </c>
+      <c r="E2119">
         <f t="shared" si="61"/>
         <v>1</v>
       </c>

--- a/CDD/Data temperatures.xlsx
+++ b/CDD/Data temperatures.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\gvaps1\USR6\CHGE\desktop\Fuel dashboard\CDD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD73DB6E-03A8-43FF-8608-1A58DF10AEE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3A5895F-CC1C-44DE-AC7E-76907A3CBFB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{805FC610-D0B7-4151-AF7A-494C14C34CCD}"/>
   </bookViews>
@@ -488,7 +488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDF6C800-FC25-4C64-B3CE-5880A9630BFD}">
-  <dimension ref="A1:E2119"/>
+  <dimension ref="A1:E2126"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.140625" customWidth="1"/>
@@ -548,14 +548,14 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <f>_xll.BDH(B$4,B$6,$B1,$B2,"Dir=V","Per=D","Days=A","Dts=S","cols=2;rows=2113")</f>
+        <f>_xll.BDH(B$4,B$6,$B1,$B2,"Dir=V","Per=D","Days=A","Dts=S","cols=2;rows=2120")</f>
         <v>43831</v>
       </c>
       <c r="B7">
         <v>13.43</v>
       </c>
       <c r="C7">
-        <f>_xll.BDH(C$4,C$6,$B1,$B2,"Dir=V","Per=D","Days=A","Dts=H","cols=1;rows=2113")</f>
+        <f>_xll.BDH(C$4,C$6,$B1,$B2,"Dir=V","Per=D","Days=A","Dts=H","cols=1;rows=2120")</f>
         <v>18.16</v>
       </c>
       <c r="D7">
@@ -40440,7 +40440,7 @@
         <v>33.47</v>
       </c>
       <c r="D2106">
-        <f t="shared" ref="D2106:E2119" si="61">IF(B2106&gt;18,1,0)</f>
+        <f t="shared" ref="D2106:E2121" si="61">IF(B2106&gt;18,1,0)</f>
         <v>1</v>
       </c>
       <c r="E2106">
@@ -40681,10 +40681,10 @@
         <v>45943</v>
       </c>
       <c r="B2119">
-        <v>23.1</v>
+        <v>22.86</v>
       </c>
       <c r="C2119">
-        <v>28.93</v>
+        <v>29.68</v>
       </c>
       <c r="D2119">
         <f t="shared" si="61"/>
@@ -40692,6 +40692,139 @@
       </c>
       <c r="E2119">
         <f t="shared" si="61"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2120" s="2">
+        <v>45944</v>
+      </c>
+      <c r="B2120">
+        <v>22.74</v>
+      </c>
+      <c r="C2120">
+        <v>29.06</v>
+      </c>
+      <c r="D2120">
+        <f t="shared" si="61"/>
+        <v>1</v>
+      </c>
+      <c r="E2120">
+        <f t="shared" si="61"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2121" s="2">
+        <v>45945</v>
+      </c>
+      <c r="B2121">
+        <v>22.54</v>
+      </c>
+      <c r="C2121">
+        <v>28.71</v>
+      </c>
+      <c r="D2121">
+        <f t="shared" si="61"/>
+        <v>1</v>
+      </c>
+      <c r="E2121">
+        <f t="shared" si="61"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2122" s="2">
+        <v>45946</v>
+      </c>
+      <c r="B2122">
+        <v>22.54</v>
+      </c>
+      <c r="C2122">
+        <v>28.46</v>
+      </c>
+      <c r="D2122">
+        <f t="shared" ref="D2122:E2126" si="62">IF(B2122&gt;18,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="E2122">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2123" s="2">
+        <v>45947</v>
+      </c>
+      <c r="B2123">
+        <v>22.71</v>
+      </c>
+      <c r="C2123">
+        <v>28.31</v>
+      </c>
+      <c r="D2123">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+      <c r="E2123">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2124" s="2">
+        <v>45948</v>
+      </c>
+      <c r="B2124">
+        <v>22.54</v>
+      </c>
+      <c r="C2124">
+        <v>28.84</v>
+      </c>
+      <c r="D2124">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+      <c r="E2124">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2125" s="2">
+        <v>45949</v>
+      </c>
+      <c r="B2125">
+        <v>22.69</v>
+      </c>
+      <c r="C2125">
+        <v>28.53</v>
+      </c>
+      <c r="D2125">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+      <c r="E2125">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2126" s="2">
+        <v>45950</v>
+      </c>
+      <c r="B2126">
+        <v>22.69</v>
+      </c>
+      <c r="C2126">
+        <v>28.53</v>
+      </c>
+      <c r="D2126">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+      <c r="E2126">
+        <f t="shared" si="62"/>
         <v>1</v>
       </c>
     </row>

--- a/CDD/Data temperatures.xlsx
+++ b/CDD/Data temperatures.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\gvaps1\USR6\CHGE\desktop\Fuel dashboard\CDD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3A5895F-CC1C-44DE-AC7E-76907A3CBFB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98B5E1F5-CE95-4370-8297-EA4835A809F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{805FC610-D0B7-4151-AF7A-494C14C34CCD}"/>
   </bookViews>
@@ -488,7 +488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDF6C800-FC25-4C64-B3CE-5880A9630BFD}">
-  <dimension ref="A1:E2126"/>
+  <dimension ref="A1:E2128"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.140625" customWidth="1"/>
@@ -547,15 +547,15 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
-        <f>_xll.BDH(B$4,B$6,$B1,$B2,"Dir=V","Per=D","Days=A","Dts=S","cols=2;rows=2120")</f>
-        <v>43831</v>
+      <c r="A7" s="2" t="str">
+        <f>_xll.BDH(B$4,B$6,$B1,$B2,"Dir=V","Per=D","Days=A","Dts=S","cols=2;rows=2122")</f>
+        <v>#N/A Requesting Data...</v>
       </c>
       <c r="B7">
         <v>13.43</v>
       </c>
       <c r="C7">
-        <f>_xll.BDH(C$4,C$6,$B1,$B2,"Dir=V","Per=D","Days=A","Dts=H","cols=1;rows=2120")</f>
+        <f>_xll.BDH(C$4,C$6,$B1,$B2,"Dir=V","Per=D","Days=A","Dts=H","cols=1;rows=2122")</f>
         <v>18.16</v>
       </c>
       <c r="D7">
@@ -40744,7 +40744,7 @@
         <v>28.46</v>
       </c>
       <c r="D2122">
-        <f t="shared" ref="D2122:E2126" si="62">IF(B2122&gt;18,1,0)</f>
+        <f t="shared" ref="D2122:E2128" si="62">IF(B2122&gt;18,1,0)</f>
         <v>1</v>
       </c>
       <c r="E2122">
@@ -40814,16 +40814,54 @@
         <v>45950</v>
       </c>
       <c r="B2126">
-        <v>22.69</v>
+        <v>24.01</v>
       </c>
       <c r="C2126">
-        <v>28.53</v>
+        <v>28.25</v>
       </c>
       <c r="D2126">
         <f t="shared" si="62"/>
         <v>1</v>
       </c>
       <c r="E2126">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2127" s="2">
+        <v>45951</v>
+      </c>
+      <c r="B2127">
+        <v>24.43</v>
+      </c>
+      <c r="C2127">
+        <v>28.12</v>
+      </c>
+      <c r="D2127">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+      <c r="E2127">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2128" s="2">
+        <v>45952</v>
+      </c>
+      <c r="B2128">
+        <v>24.43</v>
+      </c>
+      <c r="C2128">
+        <v>28.12</v>
+      </c>
+      <c r="D2128">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+      <c r="E2128">
         <f t="shared" si="62"/>
         <v>1</v>
       </c>

--- a/CDD/Data temperatures.xlsx
+++ b/CDD/Data temperatures.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\gvaps1\USR6\CHGE\desktop\Fuel dashboard\CDD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98B5E1F5-CE95-4370-8297-EA4835A809F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D35F1EE9-0559-4AD0-9D63-9490C7380ACA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{805FC610-D0B7-4151-AF7A-494C14C34CCD}"/>
   </bookViews>
@@ -488,7 +488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDF6C800-FC25-4C64-B3CE-5880A9630BFD}">
-  <dimension ref="A1:E2128"/>
+  <dimension ref="A1:E2133"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.140625" customWidth="1"/>
@@ -547,15 +547,15 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="str">
-        <f>_xll.BDH(B$4,B$6,$B1,$B2,"Dir=V","Per=D","Days=A","Dts=S","cols=2;rows=2122")</f>
-        <v>#N/A Requesting Data...</v>
+      <c r="A7" s="2">
+        <f>_xll.BDH(B$4,B$6,$B1,$B2,"Dir=V","Per=D","Days=A","Dts=S","cols=2;rows=2127")</f>
+        <v>43831</v>
       </c>
       <c r="B7">
         <v>13.43</v>
       </c>
       <c r="C7">
-        <f>_xll.BDH(C$4,C$6,$B1,$B2,"Dir=V","Per=D","Days=A","Dts=H","cols=1;rows=2122")</f>
+        <f>_xll.BDH(C$4,C$6,$B1,$B2,"Dir=V","Per=D","Days=A","Dts=H","cols=1;rows=2127")</f>
         <v>18.16</v>
       </c>
       <c r="D7">
@@ -40744,7 +40744,7 @@
         <v>28.46</v>
       </c>
       <c r="D2122">
-        <f t="shared" ref="D2122:E2128" si="62">IF(B2122&gt;18,1,0)</f>
+        <f t="shared" ref="D2122:E2133" si="62">IF(B2122&gt;18,1,0)</f>
         <v>1</v>
       </c>
       <c r="E2122">
@@ -40852,16 +40852,111 @@
         <v>45952</v>
       </c>
       <c r="B2128">
-        <v>24.43</v>
+        <v>25.4</v>
       </c>
       <c r="C2128">
-        <v>28.12</v>
+        <v>27.71</v>
       </c>
       <c r="D2128">
         <f t="shared" si="62"/>
         <v>1</v>
       </c>
       <c r="E2128">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2129" s="2">
+        <v>45953</v>
+      </c>
+      <c r="B2129">
+        <v>24.77</v>
+      </c>
+      <c r="C2129">
+        <v>27.13</v>
+      </c>
+      <c r="D2129">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+      <c r="E2129">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2130" s="2">
+        <v>45954</v>
+      </c>
+      <c r="B2130">
+        <v>24.41</v>
+      </c>
+      <c r="C2130">
+        <v>27.01</v>
+      </c>
+      <c r="D2130">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+      <c r="E2130">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2131" s="2">
+        <v>45955</v>
+      </c>
+      <c r="B2131">
+        <v>24.91</v>
+      </c>
+      <c r="C2131">
+        <v>27.3</v>
+      </c>
+      <c r="D2131">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+      <c r="E2131">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2132" s="2">
+        <v>45956</v>
+      </c>
+      <c r="B2132">
+        <v>24.91</v>
+      </c>
+      <c r="C2132">
+        <v>27.3</v>
+      </c>
+      <c r="D2132">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+      <c r="E2132">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2133" s="2">
+        <v>45957</v>
+      </c>
+      <c r="B2133">
+        <v>24.91</v>
+      </c>
+      <c r="C2133">
+        <v>27.3</v>
+      </c>
+      <c r="D2133">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+      <c r="E2133">
         <f t="shared" si="62"/>
         <v>1</v>
       </c>

--- a/CDD/Data temperatures.xlsx
+++ b/CDD/Data temperatures.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\gvaps1\USR6\CHGE\desktop\Fuel dashboard\CDD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D35F1EE9-0559-4AD0-9D63-9490C7380ACA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58597FC4-6D68-4725-B90F-4DF5663E851F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{805FC610-D0B7-4151-AF7A-494C14C34CCD}"/>
   </bookViews>
@@ -488,7 +488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDF6C800-FC25-4C64-B3CE-5880A9630BFD}">
-  <dimension ref="A1:E2133"/>
+  <dimension ref="A1:E2140"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.140625" customWidth="1"/>
@@ -548,14 +548,14 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <f>_xll.BDH(B$4,B$6,$B1,$B2,"Dir=V","Per=D","Days=A","Dts=S","cols=2;rows=2127")</f>
+        <f>_xll.BDH(B$4,B$6,$B1,$B2,"Dir=V","Per=D","Days=A","Dts=S","cols=2;rows=2134")</f>
         <v>43831</v>
       </c>
       <c r="B7">
         <v>13.43</v>
       </c>
       <c r="C7">
-        <f>_xll.BDH(C$4,C$6,$B1,$B2,"Dir=V","Per=D","Days=A","Dts=H","cols=1;rows=2127")</f>
+        <f>_xll.BDH(C$4,C$6,$B1,$B2,"Dir=V","Per=D","Days=A","Dts=H","cols=1;rows=2134")</f>
         <v>18.16</v>
       </c>
       <c r="D7">
@@ -40744,7 +40744,7 @@
         <v>28.46</v>
       </c>
       <c r="D2122">
-        <f t="shared" ref="D2122:E2133" si="62">IF(B2122&gt;18,1,0)</f>
+        <f t="shared" ref="D2122:E2137" si="62">IF(B2122&gt;18,1,0)</f>
         <v>1</v>
       </c>
       <c r="E2122">
@@ -40928,10 +40928,10 @@
         <v>45956</v>
       </c>
       <c r="B2132">
-        <v>24.91</v>
+        <v>23.96</v>
       </c>
       <c r="C2132">
-        <v>27.3</v>
+        <v>27.39</v>
       </c>
       <c r="D2132">
         <f t="shared" si="62"/>
@@ -40947,10 +40947,10 @@
         <v>45957</v>
       </c>
       <c r="B2133">
-        <v>24.91</v>
+        <v>23.35</v>
       </c>
       <c r="C2133">
-        <v>27.3</v>
+        <v>27.27</v>
       </c>
       <c r="D2133">
         <f t="shared" si="62"/>
@@ -40958,6 +40958,139 @@
       </c>
       <c r="E2133">
         <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2134" s="2">
+        <v>45958</v>
+      </c>
+      <c r="B2134">
+        <v>22.79</v>
+      </c>
+      <c r="C2134">
+        <v>26.94</v>
+      </c>
+      <c r="D2134">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+      <c r="E2134">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2135" s="2">
+        <v>45959</v>
+      </c>
+      <c r="B2135">
+        <v>22.56</v>
+      </c>
+      <c r="C2135">
+        <v>26.91</v>
+      </c>
+      <c r="D2135">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+      <c r="E2135">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2136" s="2">
+        <v>45960</v>
+      </c>
+      <c r="B2136">
+        <v>22.89</v>
+      </c>
+      <c r="C2136">
+        <v>26.69</v>
+      </c>
+      <c r="D2136">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+      <c r="E2136">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2137" s="2">
+        <v>45961</v>
+      </c>
+      <c r="B2137">
+        <v>23.24</v>
+      </c>
+      <c r="C2137">
+        <v>26.2</v>
+      </c>
+      <c r="D2137">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+      <c r="E2137">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2138" s="2">
+        <v>45962</v>
+      </c>
+      <c r="B2138">
+        <v>23.33</v>
+      </c>
+      <c r="C2138">
+        <v>25.78</v>
+      </c>
+      <c r="D2138">
+        <f t="shared" ref="D2138:E2140" si="63">IF(B2138&gt;18,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="E2138">
+        <f t="shared" si="63"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2139" s="2">
+        <v>45963</v>
+      </c>
+      <c r="B2139">
+        <v>23.33</v>
+      </c>
+      <c r="C2139">
+        <v>25.78</v>
+      </c>
+      <c r="D2139">
+        <f t="shared" si="63"/>
+        <v>1</v>
+      </c>
+      <c r="E2139">
+        <f t="shared" si="63"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2140" s="2">
+        <v>45964</v>
+      </c>
+      <c r="B2140">
+        <v>23.33</v>
+      </c>
+      <c r="C2140">
+        <v>25.78</v>
+      </c>
+      <c r="D2140">
+        <f t="shared" si="63"/>
+        <v>1</v>
+      </c>
+      <c r="E2140">
+        <f t="shared" si="63"/>
         <v>1</v>
       </c>
     </row>
